--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486300_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486300_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.484999999999999</v>
+        <v>9.854200000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5188</v>
+        <v>8.257899999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9662</v>
+        <v>1.5964</v>
       </c>
       <c r="G2" t="n">
         <v>3.8914</v>
@@ -610,13 +610,13 @@
         <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4917</v>
+        <v>-0.1226</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0959</v>
+        <v>-0.3569</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6042</v>
+        <v>0.2343</v>
       </c>
       <c r="V2" t="n">
         <v>4.3454</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5015</v>
+        <v>5.8608</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8114</v>
+        <v>3.9859</v>
       </c>
       <c r="F3" t="n">
-        <v>1.69</v>
+        <v>1.875</v>
       </c>
       <c r="G3" t="n">
         <v>2.6522</v>
@@ -688,13 +688,13 @@
         <v>0.87</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9368</v>
+        <v>0.2962</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7367</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2002</v>
+        <v>0.3851</v>
       </c>
       <c r="V3" t="n">
         <v>2.2599</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6668</v>
+        <v>3.1468</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5033</v>
+        <v>0.1925</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1701</v>
+        <v>2.9543</v>
       </c>
       <c r="G4" t="n">
         <v>5.494</v>
@@ -766,13 +766,13 @@
         <v>2.6101</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.545</v>
+        <v>-1.065</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.6439</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0989</v>
+        <v>-0.1169</v>
       </c>
       <c r="V4" t="n">
         <v>-1.4997</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4799</v>
+        <v>2.3566</v>
       </c>
       <c r="E5" t="n">
         <v>3.0281</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5483</v>
+        <v>-0.6715</v>
       </c>
       <c r="G5" t="n">
         <v>3.2594</v>
@@ -844,13 +844,13 @@
         <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1493</v>
+        <v>-1.2726</v>
       </c>
       <c r="T5" t="n">
         <v>-0.411</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7383</v>
+        <v>-0.8616</v>
       </c>
       <c r="V5" t="n">
         <v>0.3698</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. KANDE KIELI</t>
+          <t>J. POWELL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6235</v>
+        <v>2.0604</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7529</v>
+        <v>1.636</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8706</v>
+        <v>0.4244</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1714</v>
+        <v>4.9112</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3164</v>
+        <v>2.1836</v>
       </c>
       <c r="I6" t="n">
-        <v>0.145</v>
+        <v>2.7277</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.0932</v>
+        <v>3.1105</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5776</v>
+        <v>1.0434</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5155999999999999</v>
+        <v>2.0671</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9218</v>
+        <v>1.8008</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2612</v>
+        <v>1.1402</v>
       </c>
       <c r="O6" t="n">
         <v>0.6606</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9576</v>
+        <v>-0.435</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9576</v>
+        <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5531</v>
+        <v>-0.1559</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3257</v>
+        <v>-0.1694</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8788</v>
+        <v>0.0135</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3904</v>
+        <v>-2.2599</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5204</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.13</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. POWELL</t>
+          <t>G. KANDE KIELI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3291</v>
+        <v>0.929</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1205</v>
+        <v>0.1508</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2086</v>
+        <v>0.7781</v>
       </c>
       <c r="G7" t="n">
-        <v>4.9112</v>
+        <v>-0.1714</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1836</v>
+        <v>-0.3164</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7277</v>
+        <v>0.145</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1105</v>
+        <v>-1.0932</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0434</v>
+        <v>-0.5776</v>
       </c>
       <c r="L7" t="n">
-        <v>2.0671</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>1.8008</v>
+        <v>0.9218</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1402</v>
+        <v>0.2612</v>
       </c>
       <c r="O7" t="n">
         <v>0.6606</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.435</v>
+        <v>1.9576</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.87</v>
+        <v>1.9576</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8872</v>
+        <v>-1.2477</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.2764</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2023</v>
+        <v>-0.9713000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.2599</v>
+        <v>0.3904</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.5204</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.2599</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="8">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0139</v>
+        <v>0.144</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0128</v>
+        <v>-0.9443</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0267</v>
+        <v>1.0883</v>
       </c>
       <c r="G9" t="n">
         <v>0.1903</v>
@@ -1156,13 +1156,13 @@
         <v>0.435</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.4813</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3425</v>
+        <v>-0.274</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2689</v>
+        <v>-0.2073</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4295</v>
+        <v>-0.3187</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6174</v>
+        <v>-2.6607</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1879</v>
+        <v>2.342</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2272</v>
@@ -1234,13 +1234,13 @@
         <v>2.3926</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6373</v>
+        <v>-1.5265</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7619</v>
+        <v>-0.8051</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>1.13</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0501</v>
+        <v>-0.8206</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1598</v>
+        <v>-3.0228</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1097</v>
+        <v>2.2022</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5981</v>
@@ -1312,13 +1312,13 @@
         <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6918</v>
+        <v>-0.4623</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7619</v>
+        <v>-0.6249</v>
       </c>
       <c r="U11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1625</v>
       </c>
       <c r="V11" t="n">
         <v>0.9347</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2388</v>
+        <v>-2.1463</v>
       </c>
       <c r="E12" t="n">
         <v>-1.156</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0828</v>
+        <v>-0.9903</v>
       </c>
       <c r="G12" t="n">
         <v>-0.5985</v>
@@ -1390,13 +1390,13 @@
         <v>0.435</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9454</v>
+        <v>-0.8529</v>
       </c>
       <c r="T12" t="n">
         <v>-0.411</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5344</v>
+        <v>-0.4419</v>
       </c>
       <c r="V12" t="n">
         <v>-1.13</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>20.696</v>
+        <v>21.3809</v>
       </c>
       <c r="E13" t="n">
-        <v>9.2796</v>
+        <v>9.964599999999997</v>
       </c>
       <c r="F13" t="n">
-        <v>11.4162</v>
+        <v>11.4164</v>
       </c>
       <c r="G13" t="n">
         <v>16.3355</v>
@@ -1468,10 +1468,10 @@
         <v>14.1379</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.792899999999999</v>
+        <v>-7.108099999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.119199999999999</v>
+        <v>-4.4342</v>
       </c>
       <c r="U13" t="n">
         <v>-2.6739</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8929</v>
+        <v>4.4439</v>
       </c>
       <c r="E14" t="n">
-        <v>5.3617</v>
+        <v>5.697</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4688</v>
+        <v>-1.2531</v>
       </c>
       <c r="G14" t="n">
         <v>3.0859</v>
@@ -1546,13 +1546,13 @@
         <v>1.305</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0669</v>
+        <v>0.618</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1899</v>
+        <v>0.1454</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2568</v>
+        <v>0.4726</v>
       </c>
       <c r="V14" t="n">
         <v>-0.5649999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6621</v>
+        <v>3.2228</v>
       </c>
       <c r="E15" t="n">
-        <v>5.3168</v>
+        <v>5.0933</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6547</v>
+        <v>-1.8705</v>
       </c>
       <c r="G15" t="n">
         <v>0.1414</v>
@@ -1624,13 +1624,13 @@
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9557</v>
+        <v>0.5164</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8172</v>
+        <v>0.5936</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1385</v>
+        <v>-0.0772</v>
       </c>
       <c r="V15" t="n">
         <v>1.695</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4009</v>
+        <v>-0.0733</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8079</v>
+        <v>-0.6962</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4071</v>
+        <v>0.6228</v>
       </c>
       <c r="G16" t="n">
         <v>-0.9713000000000001</v>
@@ -1702,13 +1702,13 @@
         <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5705</v>
+        <v>0.898</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1646</v>
+        <v>0.2764</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4058</v>
+        <v>0.6216</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6841</v>
+        <v>-0.2062</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4438</v>
+        <v>-0.9967</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7597</v>
+        <v>0.7905</v>
       </c>
       <c r="G17" t="n">
         <v>0.6484</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1455</v>
+        <v>0.6234</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.411</v>
+        <v>0.0361</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5565</v>
+        <v>0.5873</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3904</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7877</v>
+        <v>-1.1828</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4022</v>
+        <v>-0.2905</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3855</v>
+        <v>-0.8923</v>
       </c>
       <c r="G18" t="n">
         <v>-0.008500000000000001</v>
@@ -1858,13 +1858,13 @@
         <v>0.435</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5259</v>
+        <v>1.1308</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4951</v>
+        <v>0.6069</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0308</v>
+        <v>0.5239</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5649999999999999</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ PEREZ</t>
+          <t>R. GILL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0127</v>
+        <v>-2.2935</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1889</v>
+        <v>-2.2413</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8238</v>
+        <v>-0.0522</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5367</v>
+        <v>-1.6619</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3558</v>
+        <v>-1.7185</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.8925</v>
+        <v>0.0566</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.5964</v>
+        <v>-1.3406</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1063</v>
+        <v>-1.4171</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.4901</v>
+        <v>0.0765</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0597</v>
+        <v>-0.3213</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4621</v>
+        <v>-0.3013</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4024</v>
+        <v>-0.0199</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2175</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.6525</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8923</v>
+        <v>0.9556</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4951</v>
+        <v>0.2091</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3972</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1507</v>
+        <v>-0.9347</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.2806</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. MC DONNELL</t>
+          <t>I. VAZQUEZ PEREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2496</v>
+        <v>-2.6138</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2853</v>
+        <v>-0.6359</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9641999999999999</v>
+        <v>-1.9779</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.3152</v>
+        <v>-1.5367</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.4244</v>
+        <v>0.3558</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1092</v>
+        <v>-1.8925</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.8265</v>
+        <v>-1.5964</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.9556</v>
+        <v>-0.1063</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1292</v>
+        <v>-1.4901</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4887</v>
+        <v>0.0597</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4688</v>
+        <v>0.4621</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0199</v>
+        <v>-0.4024</v>
       </c>
       <c r="P20" t="n">
         <v>-0.2175</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0875</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4131</v>
+        <v>0.2911</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.0481</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6969</v>
+        <v>0.243</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.13</v>
+        <v>-1.1507</v>
       </c>
       <c r="W20" t="n">
         <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.2599</v>
+        <v>-2.2806</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. GILL</t>
+          <t>S. MC DONNELL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4631</v>
+        <v>-2.7274</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6884</v>
+        <v>-1.7323</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2252</v>
+        <v>-0.9951</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6619</v>
+        <v>-2.3152</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7185</v>
+        <v>-3.4244</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0566</v>
+        <v>1.1092</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3406</v>
+        <v>-1.8265</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.4171</v>
+        <v>-2.9556</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0765</v>
+        <v>1.1292</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3213</v>
+        <v>-0.4887</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3013</v>
+        <v>-0.4688</v>
       </c>
       <c r="O21" t="n">
         <v>-0.0199</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6525</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.305</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>0.786</v>
+        <v>0.9352</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2379</v>
+        <v>0.2692</v>
       </c>
       <c r="U21" t="n">
-        <v>1.024</v>
+        <v>0.666</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9347</v>
+        <v>-1.13</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.13</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. IGLESIAS FERNANDEZ</t>
+          <t>C. OKANU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9273</v>
+        <v>-3.4004</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9699</v>
+        <v>-1.8529</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0426</v>
+        <v>-1.5475</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.4996</v>
+        <v>-3.631</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.2844</v>
+        <v>-2.6246</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2152</v>
+        <v>-1.0064</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.5593</v>
+        <v>-2.0492</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.5975</v>
+        <v>-2.1257</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0382</v>
+        <v>0.0765</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0597</v>
+        <v>-1.5819</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3131</v>
+        <v>-0.4989</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2534</v>
+        <v>-1.0829</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6525</v>
+        <v>-0.87</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="S22" t="n">
-        <v>1.7898</v>
+        <v>0.5357</v>
       </c>
       <c r="T22" t="n">
-        <v>1.4817</v>
+        <v>0.1538</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3081</v>
+        <v>0.3818</v>
       </c>
       <c r="V22" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X22" t="n">
         <v>-0.5649999999999999</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0.1952</v>
-      </c>
-      <c r="X22" t="n">
-        <v>-0.7602</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5015</v>
+        <v>-3.5245</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6279</v>
+        <v>-3.4044</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1265</v>
+        <v>-0.1201</v>
       </c>
       <c r="G23" t="n">
         <v>-2.611</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5891</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2379</v>
+        <v>-0.0144</v>
       </c>
       <c r="U23" t="n">
-        <v>0.827</v>
+        <v>0.5804</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1745</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C. OKANU</t>
+          <t>M. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6432</v>
+        <v>-4.3416</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1882</v>
+        <v>-4.1992</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.455</v>
+        <v>-0.1423</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.631</v>
+        <v>-3.4996</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.6246</v>
+        <v>-3.2844</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.0064</v>
+        <v>-0.2152</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.0492</v>
+        <v>-3.5593</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.1257</v>
+        <v>-3.5975</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0765</v>
+        <v>0.0382</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5819</v>
+        <v>0.0597</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4989</v>
+        <v>0.3131</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0829</v>
+        <v>-0.2534</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.87</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q24" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2929</v>
+        <v>0.3755</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1815</v>
+        <v>0.2524</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4743</v>
+        <v>0.1232</v>
       </c>
       <c r="V24" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.5809</v>
+        <v>-7.999</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.4923</v>
+        <v>-6.157</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.0886</v>
+        <v>-1.842</v>
       </c>
       <c r="G25" t="n">
         <v>-3.976</v>
@@ -2404,13 +2404,13 @@
         <v>0.435</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2346</v>
+        <v>0.3473</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2379</v>
+        <v>0.0973</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0034</v>
+        <v>0.2499</v>
       </c>
       <c r="V25" t="n">
         <v>-1.3252</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-20.696</v>
+        <v>-20.6958</v>
       </c>
       <c r="E26" t="n">
-        <v>-11.4163</v>
+        <v>-11.4161</v>
       </c>
       <c r="F26" t="n">
-        <v>-9.279499999999999</v>
+        <v>-9.2797</v>
       </c>
       <c r="G26" t="n">
         <v>-16.3355</v>
@@ -2467,7 +2467,7 @@
         <v>-8.627599999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>-3.013399999999999</v>
+        <v>-3.0134</v>
       </c>
       <c r="O26" t="n">
         <v>-5.613799999999999</v>
@@ -2482,13 +2482,13 @@
         <v>6.524999999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>7.793099999999999</v>
+        <v>7.793</v>
       </c>
       <c r="T26" t="n">
-        <v>2.673800000000001</v>
+        <v>2.6739</v>
       </c>
       <c r="U26" t="n">
-        <v>5.119300000000001</v>
+        <v>5.119000000000001</v>
       </c>
       <c r="V26" t="n">
         <v>-4.5405</v>
